--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +409,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -436,83 +436,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>78759.93</t>
+          <t>640000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>78759.93</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>49580</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>17179.93</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>29179.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -409,12 +409,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -436,12 +436,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -463,83 +463,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>78759.93</t>
+          <t>640000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>78759.93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>69580</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>29179.93</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9179.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,12 +409,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -436,12 +436,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -463,12 +463,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -490,83 +490,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>78759.93</t>
+          <t>640000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>69580</t>
+          <t>78759.93</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>78757</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>9179.93</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -436,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -451,7 +466,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -463,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -478,7 +493,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -490,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -517,83 +532,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>640000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78759.93</t>
+          <t>690000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>84857.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>78757</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2.93</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6100.5</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -532,12 +532,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -559,83 +559,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>690000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>84857.5</t>
+          <t>690000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>84857.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>79145</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>6100.5</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5712.5</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -532,12 +532,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -559,12 +559,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -586,83 +586,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>690000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>84857.5</t>
+          <t>690000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79145</t>
+          <t>84857.5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>84854</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5712.5</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.5</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -505,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -532,12 +547,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -547,7 +562,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -559,12 +574,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -574,7 +589,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -586,12 +601,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -613,83 +628,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>690000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>84857.5</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>84854</t>
+          <t>98110.51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>84854</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3.5</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13256.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,12 +547,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -574,12 +574,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -628,12 +628,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -655,83 +655,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>800000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>98110.51</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>84854</t>
+          <t>98110.51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>98107</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>13256.51</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -574,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -601,12 +616,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -616,7 +631,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -628,12 +643,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -643,7 +658,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -655,12 +670,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -682,83 +697,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>800000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>98110.51</t>
+          <t>875000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>98107</t>
+          <t>107256.85</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>98107</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3.51</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>9149.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,12 +616,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -670,12 +670,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -697,12 +697,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -724,83 +724,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>875000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>107256.85</t>
+          <t>875000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>98107</t>
+          <t>107256.85</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>99107</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>9149.85</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8149.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,12 +616,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -670,12 +670,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -697,12 +697,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -724,12 +724,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -751,83 +751,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>875000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>107256.85</t>
+          <t>875000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>99107</t>
+          <t>107256.85</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>107253</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>8149.85</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 15:56:45</t>
+          <t>09/03 10:39:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -670,12 +685,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -697,12 +712,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -712,7 +727,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -724,12 +739,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -739,7 +754,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -751,12 +766,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -778,83 +793,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>875000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>107256.85</t>
+          <t>1005000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>107253</t>
+          <t>123506.85</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>107253</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3.85</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16253.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 10:39:51</t>
+          <t>09/03 12:10:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16250</t>
+          <t>11515.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 15:56:45</t>
+          <t>09/03 10:39:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -712,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -739,12 +754,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -754,7 +769,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -766,12 +781,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -781,7 +796,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -793,12 +808,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -820,83 +835,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1005000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>123506.85</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>107253</t>
+          <t>135022</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>107253</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>16253.85</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>27769</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>09/03 13:33:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -808,12 +808,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -835,12 +835,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -862,83 +862,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>135022</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>107253</t>
+          <t>135022</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>135018</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>27769</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 12:10:27</t>
+          <t>09/04 17:02:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11515.15</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 10:39:51</t>
+          <t>09/03 12:10:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16250</t>
+          <t>11515.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 15:56:45</t>
+          <t>09/03 10:39:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 13:33:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>09/03 13:33:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -781,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -808,12 +823,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -823,7 +838,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -835,12 +850,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -850,7 +865,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -862,12 +877,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -889,83 +904,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>135022</t>
+          <t>1170000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>135018</t>
+          <t>143772</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>135018</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>8754</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 13:33:33</t>
+          <t>09/04 18:26:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>09/03 13:33:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,12 +823,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -850,12 +850,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -877,12 +877,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -904,12 +904,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -931,83 +931,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>143772</t>
+          <t>1170000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>135018</t>
+          <t>143772</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>143768</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>8754</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 17:02:30</t>
+          <t>09/05 16:45:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 12:10:27</t>
+          <t>09/04 17:02:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11515.15</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 10:39:51</t>
+          <t>09/03 12:10:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16250</t>
+          <t>11515.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 15:56:45</t>
+          <t>09/03 10:39:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/23 09:55:39</t>
+          <t>08/27 16:30:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>17177.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/19 14:13:27</t>
+          <t>08/23 09:55:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/19 14:13:27</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18404.91</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/18 10:56:11</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>250000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>31055.9</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>kaikai99666</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/04 18:26:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 13:33:33</t>
+          <t>09/04 18:26:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>09/03 13:33:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -850,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -877,12 +892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -892,7 +907,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -904,12 +919,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -919,7 +934,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -931,12 +946,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -958,83 +973,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>143772</t>
+          <t>1220000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>143768</t>
+          <t>150022</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>143768</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6254</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/04 18:26:30</t>
+          <t>09/05 19:09:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 13:33:33</t>
+          <t>09/04 18:26:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/02 17:32:46</t>
+          <t>09/03 13:33:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
+          <t>09/02 17:32:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/30 16:00:09</t>
+          <t>09/02 17:30:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/28 16:33:50</t>
+          <t>08/30 16:00:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
+          <t>08/28 16:33:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 19:09:36</t>
+          <t>08/28 11:20:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>08/27 18:02:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/23 11:03:54</t>
+          <t>08/27 16:31:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -919,12 +919,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/23 09:55:43</t>
+          <t>08/23 11:03:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/19 15:36:05</t>
+          <t>08/23 09:55:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/19 15:34:34</t>
+          <t>08/19 15:36:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1000,83 +1000,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>08/19 15:34:34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>08/18 12:26:54</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>31055</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>150022</t>
+          <t>1220000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>143768</t>
+          <t>150022</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>150018</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6254</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
